--- a/FIXES.xlsx
+++ b/FIXES.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -608,12 +608,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Require, for each risk named, a verbatim quotation from that strategy's own text that states the connection, emitted in a risk_evidence field beside related_risks. Cap at three risks unless the plan explicitly names more. Say that a standing function of the state (defence, debt service, pensions, general administration) is not a risk response unless the plan frames it as one. Then a new check, A18, fails any related_risks entry with no quotation behind it, which makes the rule enforceable rather than hoped for.</t>
+          <t>Require, for each risk named, a verbatim quotation from that strategy's own text that states the connection, emitted in a risk_evidence field beside related_risks. Cap at three risks unless the plan explicitly names more. Say that a standing function of the state (defence, debt service, pensions, general administration) is not a risk response unless the plan frames it as one. Then a new check, A19, fails any related_risks entry with no quotation behind it, which makes the rule enforceable rather than hoped for.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>01_Pipeline/prompts/4_strategy_clean.txt, 02_Automation/schemas.py (STAGE4_FIELDS), 01_Pipeline/scripts/audit_checks.py (A18), 01_Pipeline/scripts/build_final_panel.py (carry risk_evidence)</t>
+          <t>01_Pipeline/prompts/4_strategy_clean.txt, 02_Automation/schemas.py (STAGE4_FIELDS), 01_Pipeline/scripts/audit_checks.py (A19), 01_Pipeline/scripts/build_final_panel.py (carry risk_evidence)</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -640,47 +640,47 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>F6</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Prompt 5, budget extraction</t>
+          <t>Prompt 4, strategy clean</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Brunei yields one usable budget year out of four documents, and budget line names leak into the strategy inventory</t>
+          <t>Budget programme names come back out of stage 4 as plan strategies, then match 'their' programme perfectly</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Brunei's budget is a speech, not a table. Prompt 5 is written for a tabulated budget: it looks for programme rows with codes and amounts, finds few, and the gap is then filled from the budget side of the mapping, which puts budget line names into the strategy column.</t>
+          <t>run_stage4 injects the budget programme list into Prompt 4 as the target granularity, which is right: it is how a strategy lands on a fundable unit. But nothing forbids the model from ANSWERING with a bucket name when it has no plan material to consolidate. Brunei's NDP text is a speech, stage 3 recovers little, and four strategies came back that are budget lines wearing a strategy's clothes.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>A second budget-extraction prompt for narrative budgets, selected per country by a documents.style flag in the country config. It reads prose ('The amount of X million will be allocated to Y'), emits the same schema, and marks each row with the sentence it came from so source fidelity can still check it. China's budget has the same shape, so the prompt is needed twice over.</t>
+          <t>Two lines in Prompt 4: a strategy must consolidate at least one intervention from the row-level table, and the budget programme list is a target to map ONTO, never a source to draw names from. Check A18 already fails any strategyclean row with no component intervention, so the rule is enforced rather than hoped for. A18 is advisory today; promote it to a gate once Brunei is re-run.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>01_Pipeline/prompts/5b_budget_transcript.txt (new), 02_Automation/stages.py (stage 5 selects the prompt), 01_Pipeline/countries/*.json (documents.style)</t>
+          <t>01_Pipeline/prompts/4_strategy_clean.txt, 01_Pipeline/scripts/audit_checks.py (A18, already added)</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>One new prompt plus a re-run of stage 5 for Brunei's four documents.</t>
+          <t>Re-run stage 4 for Brunei. Thailand and Brazil already pass A18, so they need no re-run for this.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Brunei stays a one-year country and its 97.4% coverage figure keeps resting on a single speech.</t>
+          <t>Brunei's page shows budget lines as plan strategies with confident rationales, and its 97.4% of budget mapped is partly the budget matching itself.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -690,54 +690,54 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>W3, W4</t>
+          <t>W3, W6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>F4</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Prompt 3, intervention extraction</t>
+          <t>Prompt 5, budget extraction</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11.5% of intervention_evidence quotations are paraphrases rather than the plan's own words</t>
+          <t>Brunei yields one usable budget year out of four documents, and budget line names leak into the strategy inventory</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Prompt 3 asks for evidence and does not say that the evidence must be a substring of the source. The model summarises where the sentence is long.</t>
+          <t>Brunei's budget is a speech, not a table. Prompt 5 is written for a tabulated budget: it looks for programme rows with codes and amounts, finds few, and the gap is then filled from the budget side of the mapping, which puts budget line names into the strategy column.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>State that intervention_evidence must be copied character for character, and that a quotation that cannot be copied verbatim should be shortened rather than reworded. validate_evidence_quotes already measures this, so the fix is verifiable the moment it runs.</t>
+          <t>A second budget-extraction prompt for narrative budgets, selected per country by a documents.style flag in the country config. It reads prose ('The amount of X million will be allocated to Y'), emits the same schema, and marks each row with the sentence it came from so source fidelity can still check it. China's budget has the same shape, so the prompt is needed twice over.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>01_Pipeline/prompts/3_strategy_extraction.txt</t>
+          <t>01_Pipeline/prompts/5b_budget_transcript.txt (new), 02_Automation/stages.py (stage 5 selects the prompt), 01_Pipeline/countries/*.json (documents.style)</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Re-run stage 3 per country.</t>
+          <t>One new prompt plus a re-run of stage 5 for Brunei's four documents.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>A reviewer checking a quotation against the plan finds words that are not there and stops trusting the rest.</t>
+          <t>Brunei stays a one-year country and its 97.4% coverage figure keeps resting on a single speech.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -745,60 +745,117 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>W3, W4</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Prompt 3, intervention extraction</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11.5% of intervention_evidence quotations are paraphrases rather than the plan's own words</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Prompt 3 asks for evidence and does not say that the evidence must be a substring of the source. The model summarises where the sentence is long.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>State that intervention_evidence must be copied character for character, and that a quotation that cannot be copied verbatim should be shortened rather than reworded. validate_evidence_quotes already measures this, so the fix is verifiable the moment it runs.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>01_Pipeline/prompts/3_strategy_extraction.txt</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Re-run stage 3 per country.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>A reviewer checking a quotation against the plan finds words that are not there and stops trusting the rest.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>F5</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Supabase</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>maturity_summary has no view behind it, so the database cannot reproduce six of its eight metrics</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>0004_maturity_subtypes.sql was written and never applied: it needs either a service token or a paste into the SQL editor.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Apply the migration, then confirm audit_checks A12 and build_dashboard_from_db --verify agree with the sheet.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>03_Ingest_and_Publishing/supabase/migrations/0004_maturity_subtypes.sql</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>None beyond applying it.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>The database round trip stays unfaithful for the maturity metrics.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>BLOCKED, needs a token or a paste</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -829,7 +886,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-13 08:23 from 04_Docs_and_Planning/fixes.json</t>
+          <t>Generated 2026-08-13 11:43 from 04_Docs_and_Planning/fixes.json</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/FIXES.xlsx
+++ b/FIXES.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -697,12 +697,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -712,32 +712,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Brunei yields one usable budget year out of four documents, and budget line names leak into the strategy inventory</t>
+          <t>Two countries' budget figures come from a prompt version that has been superseded</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Brunei's budget is a speech, not a table. Prompt 5 is written for a tabulated budget: it looks for programme rows with codes and amounts, finds few, and the gap is then filled from the budget side of the mapping, which puts budget line names into the strategy column.</t>
+          <t>Prompt 5 gained rules 3a and 4a on 2026-08-12 after Thailand's FY2024 was found to be missing programmes 2.14 and 2.15, whose table rows wrap and whose amounts are printed in the narrative. Only Thailand was re-run. Nothing in the pipeline compared an output's date with its prompt's, so the gap was invisible.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>A second budget-extraction prompt for narrative budgets, selected per country by a documents.style flag in the country config. It reads prose ('The amount of X million will be allocated to Y'), emits the same schema, and marks each row with the sentence it came from so source fidelity can still check it. China's budget has the same shape, so the prompt is needed twice over.</t>
+          <t>Re-run stage 5 for Brazil (2021, 2024) and Brunei (2021, 2022, 2025, 2026), then run_pipeline for both. Detector D12 already reports the condition; promote it to a gate once both are current.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>01_Pipeline/prompts/5b_budget_transcript.txt (new), 02_Automation/stages.py (stage 5 selects the prompt), 01_Pipeline/countries/*.json (documents.style)</t>
+          <t>02_Automation/run_llm_pipeline.py --stages 5 --force, then 01_Pipeline/scripts/run_pipeline.py</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>One new prompt plus a re-run of stage 5 for Brunei's four documents.</t>
+          <t>Six budget documents through stage 5. Brunei's four are speeches and will still extract poorly until F3 lands, so Brazil's two are the ones that will actually change figures.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Brunei stays a one-year country and its 97.4% coverage figure keeps resting on a single speech.</t>
+          <t>Brunei's two unreconciled strategy-years stay unexplained, and Brazil's coverage may be understated by whatever the old prompt skipped.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -747,54 +747,54 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>W3, W4</t>
+          <t>W7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>F4</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Prompt 3, intervention extraction</t>
+          <t>Prompt 5, budget extraction</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11.5% of intervention_evidence quotations are paraphrases rather than the plan's own words</t>
+          <t>Brunei yields one usable budget year out of four documents, and budget line names leak into the strategy inventory</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Prompt 3 asks for evidence and does not say that the evidence must be a substring of the source. The model summarises where the sentence is long.</t>
+          <t>Brunei's budget is a speech, not a table. Prompt 5 is written for a tabulated budget: it looks for programme rows with codes and amounts, finds few, and the gap is then filled from the budget side of the mapping, which puts budget line names into the strategy column.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>State that intervention_evidence must be copied character for character, and that a quotation that cannot be copied verbatim should be shortened rather than reworded. validate_evidence_quotes already measures this, so the fix is verifiable the moment it runs.</t>
+          <t>A second budget-extraction prompt for narrative budgets, selected per country by a documents.style flag in the country config. It reads prose ('The amount of X million will be allocated to Y'), emits the same schema, and marks each row with the sentence it came from so source fidelity can still check it. China's budget has the same shape, so the prompt is needed twice over.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>01_Pipeline/prompts/3_strategy_extraction.txt</t>
+          <t>01_Pipeline/prompts/5b_budget_transcript.txt (new), 02_Automation/stages.py (stage 5 selects the prompt), 01_Pipeline/countries/*.json (documents.style)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Re-run stage 3 per country.</t>
+          <t>One new prompt plus a re-run of stage 5 for Brunei's four documents.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>A reviewer checking a quotation against the plan finds words that are not there and stops trusting the rest.</t>
+          <t>Brunei stays a one-year country and its 97.4% coverage figure keeps resting on a single speech.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -802,60 +802,117 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>W3, W4</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Prompt 3, intervention extraction</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11.5% of intervention_evidence quotations are paraphrases rather than the plan's own words</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Prompt 3 asks for evidence and does not say that the evidence must be a substring of the source. The model summarises where the sentence is long.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>State that intervention_evidence must be copied character for character, and that a quotation that cannot be copied verbatim should be shortened rather than reworded. validate_evidence_quotes already measures this, so the fix is verifiable the moment it runs.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>01_Pipeline/prompts/3_strategy_extraction.txt</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Re-run stage 3 per country.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>A reviewer checking a quotation against the plan finds words that are not there and stops trusting the rest.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>F5</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Supabase</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>maturity_summary has no view behind it, so the database cannot reproduce six of its eight metrics</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>0004_maturity_subtypes.sql was written and never applied: it needs either a service token or a paste into the SQL editor.</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Apply the migration, then confirm audit_checks A12 and build_dashboard_from_db --verify agree with the sheet.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>03_Ingest_and_Publishing/supabase/migrations/0004_maturity_subtypes.sql</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>None beyond applying it.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>The database round trip stays unfaithful for the maturity metrics.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>BLOCKED, needs a token or a paste</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -886,7 +943,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-13 11:43 from 04_Docs_and_Planning/fixes.json</t>
+          <t>Generated 2026-08-13 15:03 from 04_Docs_and_Planning/fixes.json</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/FIXES.xlsx
+++ b/FIXES.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -754,12 +754,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>F8</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -769,32 +769,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Brunei yields one usable budget year out of four documents, and budget line names leak into the strategy inventory</t>
+          <t>A multi-year project table extracts nothing, because which column is this year's budget is never stated</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Brunei's budget is a speech, not a table. Prompt 5 is written for a tabulated budget: it looks for programme rows with codes and amounts, finds few, and the gap is then filled from the budget side of the mapping, which puts budget line names into the strategy column.</t>
+          <t>Prompt 5 assumes a budget table has one amount column and a strategy total to reconcile against. Kiribati's development budget has six year columns and no ministry totals; Thailand's FY2023 book has three. Where the assumption holds the prompt works; where it does not the model correctly declines to guess and the country produces nothing for the price of a full extraction.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>A second budget-extraction prompt for narrative budgets, selected per country by a documents.style flag in the country config. It reads prose ('The amount of X million will be allocated to Y'), emits the same schema, and marks each row with the sentence it came from so source fidelity can still check it. China's budget has the same shape, so the prompt is needed twice over.</t>
+          <t>Add an optional amount_column to the per-year budget config, passed into Prompt 5 as the column to read ('2025 Budget'), and have the prompt state that where several year columns exist it must use the named one and emit nothing rather than guess. Where no column is named and several exist, stop before spending: document_shape.py already reports the count. The reconciliation rule needs the same treatment, since a table with no printed strategy total cannot reconcile and should say so rather than fail.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>01_Pipeline/prompts/5b_budget_transcript.txt (new), 02_Automation/stages.py (stage 5 selects the prompt), 01_Pipeline/countries/*.json (documents.style)</t>
+          <t>01_Pipeline/prompts/5_budget_extraction.txt, 02_Automation/inputs/&lt;slug&gt;.json (amount_column), 02_Automation/stages.py (pass it through), 01_Pipeline/scripts/document_shape.py (already reports year columns)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>One new prompt plus a re-run of stage 5 for Brunei's four documents.</t>
+          <t>One prompt change plus a re-run of stage 5 for Kiribati, four documents, about $2.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Brunei stays a one-year country and its 97.4% coverage figure keeps resting on a single speech.</t>
+          <t>Kiribati cannot be run at all, and any country whose budget is published as a multi-year table has the same wall. On the evidence of these ten, that is a common publishing format rather than an oddity.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -804,54 +804,54 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>W3, W4</t>
+          <t>W8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>F4</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>F9</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Prompt 3, intervention extraction</t>
+          <t>orchestration</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11.5% of intervention_evidence quotations are paraphrases rather than the plan's own words</t>
+          <t>Countries are committed to a full run before anyone knows whether their budget document can be extracted at all</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Prompt 3 asks for evidence and does not say that the evidence must be a substring of the source. The model summarises where the sentence is long.</t>
+          <t>The only gate before spending was a text heuristic, and it was wrong three times in a row: Malaysia read as prose because its programme codes are six digits, Kiribati read as a usable table when its rows are catering and cleaning, Bhutan read as a usable table when its rows are corporate accounts. Each fix made the heuristic smarter without making it right, because the question is what the PROMPT will find and only the prompt can answer that.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>State that intervention_evidence must be copied character for character, and that a quotation that cannot be copied verbatim should be shortened rather than reworded. validate_evidence_quotes already measures this, so the fix is verifiable the moment it runs.</t>
+          <t>Make stage5_probe.py a required step: one budget document, 4 to 10 calls, programme rows counted per page. Wire it into the orchestrator so a country with no probe result, or a failing one, does not start. Then route by document class, since the probe also tells you WHICH class: estimates table to Prompt 5, narrative to 5b (F3), multi-year project table to 5c or a named amount column (F8), fiscal report to nothing until the right document is sourced.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>01_Pipeline/prompts/3_strategy_extraction.txt</t>
+          <t>02_Automation/stage5_probe.py (written), 02_Automation/run_llm_pipeline.py (gate on it), 02_Automation/inputs/&lt;slug&gt;.json (documents.style)</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Re-run stage 3 per country.</t>
+          <t>None to build; it saves $8 to $48 every time a country would have failed.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>A reviewer checking a quotation against the plan finds words that are not there and stops trusting the rest.</t>
+          <t>Kiribati cost $6.21 and Bhutan $2.00 to learn what $0.60 of probing would have said first.</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -859,60 +859,174 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>W8, W9</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Prompt 5, budget extraction</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Brunei yields one usable budget year out of four documents, and budget line names leak into the strategy inventory</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Brunei's budget is a speech, not a table. Prompt 5 is written for a tabulated budget: it looks for programme rows with codes and amounts, finds few, and the gap is then filled from the budget side of the mapping, which puts budget line names into the strategy column.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>A second budget-extraction prompt for narrative budgets, selected per country by a documents.style flag in the country config. It reads prose ('The amount of X million will be allocated to Y'), emits the same schema, and marks each row with the sentence it came from so source fidelity can still check it. China's budget has the same shape, so the prompt is needed twice over.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>01_Pipeline/prompts/5b_budget_transcript.txt (new), 02_Automation/stages.py (stage 5 selects the prompt), 01_Pipeline/countries/*.json (documents.style)</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>One new prompt plus a re-run of stage 5 for Brunei's four documents.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Brunei stays a one-year country and its 97.4% coverage figure keeps resting on a single speech.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>W3, W4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Prompt 3, intervention extraction</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>11.5% of intervention_evidence quotations are paraphrases rather than the plan's own words</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Prompt 3 asks for evidence and does not say that the evidence must be a substring of the source. The model summarises where the sentence is long.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>State that intervention_evidence must be copied character for character, and that a quotation that cannot be copied verbatim should be shortened rather than reworded. validate_evidence_quotes already measures this, so the fix is verifiable the moment it runs.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>01_Pipeline/prompts/3_strategy_extraction.txt</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Re-run stage 3 per country.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>A reviewer checking a quotation against the plan finds words that are not there and stops trusting the rest.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>F5</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Supabase</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>maturity_summary has no view behind it, so the database cannot reproduce six of its eight metrics</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>0004_maturity_subtypes.sql was written and never applied: it needs either a service token or a paste into the SQL editor.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Apply the migration, then confirm audit_checks A12 and build_dashboard_from_db --verify agree with the sheet.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>03_Ingest_and_Publishing/supabase/migrations/0004_maturity_subtypes.sql</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>None beyond applying it.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>The database round trip stays unfaithful for the maturity metrics.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>BLOCKED, needs a token or a paste</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -943,7 +1057,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-13 15:03 from 04_Docs_and_Planning/fixes.json</t>
+          <t>Generated 2026-08-15 09:24 from 04_Docs_and_Planning/fixes.json</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/FIXES.xlsx
+++ b/FIXES.xlsx
@@ -1057,7 +1057,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-15 09:24 from 04_Docs_and_Planning/fixes.json</t>
+          <t>Generated 2026-08-15 09:28 from 04_Docs_and_Planning/fixes.json</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/FIXES.xlsx
+++ b/FIXES.xlsx
@@ -1057,7 +1057,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-15 09:28 from 04_Docs_and_Planning/fixes.json</t>
+          <t>Generated 2026-08-15 09:42 from 04_Docs_and_Planning/fixes.json</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/FIXES.xlsx
+++ b/FIXES.xlsx
@@ -1057,7 +1057,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-15 09:42 from 04_Docs_and_Planning/fixes.json</t>
+          <t>Generated 2026-08-15 10:06 from 04_Docs_and_Planning/fixes.json</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/FIXES.xlsx
+++ b/FIXES.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -583,7 +583,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F10</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -593,37 +593,37 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Prompt 4, strategy clean</t>
+          <t>combine_budget_years</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Standing functions are tagged as responses to risks they do not address, inflating every risk chart</t>
+          <t>The programme code style is defaulted, and the wrong default silently unmaps a whole country</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Prompt 4 asks which of the eleven risks a strategy relates to and accepts topical adjacency. Nothing requires the plan to say the strategy responds to that risk, and nothing penalises tagging six risks at once.</t>
+          <t>normalize_program_code assumes hierarchical codes and prefixes a bare code with its strategy. Where codes are standalone the result matches nothing. It cost Brazil 524 edges, then Kenya 824 programme-years and Jamaica 254, each discovered separately after a full run.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Require, for each risk named, a verbatim quotation from that strategy's own text that states the connection, emitted in a risk_evidence field beside related_risks. Cap at three risks unless the plan explicitly names more. Say that a standing function of the state (defence, debt service, pensions, general administration) is not a risk response unless the plan frames it as one. Then a new check, A19, fails any related_risks entry with no quotation behind it, which makes the rule enforceable rather than hoped for.</t>
+          <t>Choose the style by measuring rather than defaulting: try both against the mapping's codes and take the one that resolves more, or refuse to build and say which style the codes look like. The evidence is already on disk at build time, so this needs no model call and no new input. Add a check that fails when more than a tenth of a country's matched codes are absent from its own budget layer.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>01_Pipeline/prompts/4_strategy_clean.txt, 02_Automation/schemas.py (STAGE4_FIELDS), 01_Pipeline/scripts/audit_checks.py (A19), 01_Pipeline/scripts/build_final_panel.py (carry risk_evidence)</t>
+          <t>01_Pipeline/scripts/combine_budget_years.py (normalize_program_code), 01_Pipeline/scripts/audit_checks.py (new check)</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Re-run stage 4 for all three countries. Stage 4 is the judgement stage, so this is the expensive one; roughly the cost of a full re-run of consolidation per country.</t>
+          <t>None. Deterministic, and it runs on data the pipeline already holds.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Every risk chart on every page overstates how much of the budget responds to each risk, and the error is invisible to every existing check.</t>
+          <t>Every new country is one silent default away from mapping nothing, and the symptom looks like a bad model rather than a bad join.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -633,14 +633,14 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>W2</t>
+          <t>W11</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>F6</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -655,32 +655,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Budget programme names come back out of stage 4 as plan strategies, then match 'their' programme perfectly</t>
+          <t>Standing functions are tagged as responses to risks they do not address, inflating every risk chart</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>run_stage4 injects the budget programme list into Prompt 4 as the target granularity, which is right: it is how a strategy lands on a fundable unit. But nothing forbids the model from ANSWERING with a bucket name when it has no plan material to consolidate. Brunei's NDP text is a speech, stage 3 recovers little, and four strategies came back that are budget lines wearing a strategy's clothes.</t>
+          <t>Prompt 4 asks which of the eleven risks a strategy relates to and accepts topical adjacency. Nothing requires the plan to say the strategy responds to that risk, and nothing penalises tagging six risks at once.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Two lines in Prompt 4: a strategy must consolidate at least one intervention from the row-level table, and the budget programme list is a target to map ONTO, never a source to draw names from. Check A18 already fails any strategyclean row with no component intervention, so the rule is enforced rather than hoped for. A18 is advisory today; promote it to a gate once Brunei is re-run.</t>
+          <t>Require, for each risk named, a verbatim quotation from that strategy's own text that states the connection, emitted in a risk_evidence field beside related_risks. Cap at three risks unless the plan explicitly names more. Say that a standing function of the state (defence, debt service, pensions, general administration) is not a risk response unless the plan frames it as one. Then a new check, A19, fails any related_risks entry with no quotation behind it, which makes the rule enforceable rather than hoped for.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>01_Pipeline/prompts/4_strategy_clean.txt, 01_Pipeline/scripts/audit_checks.py (A18, already added)</t>
+          <t>01_Pipeline/prompts/4_strategy_clean.txt, 02_Automation/schemas.py (STAGE4_FIELDS), 01_Pipeline/scripts/audit_checks.py (A19), 01_Pipeline/scripts/build_final_panel.py (carry risk_evidence)</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Re-run stage 4 for Brunei. Thailand and Brazil already pass A18, so they need no re-run for this.</t>
+          <t>Re-run stage 4 for all three countries. Stage 4 is the judgement stage, so this is the expensive one; roughly the cost of a full re-run of consolidation per country.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Brunei's page shows budget lines as plan strategies with confident rationales, and its 97.4% of budget mapped is partly the budget matching itself.</t>
+          <t>Every risk chart on every page overstates how much of the budget responds to each risk, and the error is invisible to every existing check.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -690,14 +690,14 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>W3, W6</t>
+          <t>W2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>F7</t>
+          <t>F6</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -707,37 +707,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Prompt 5, budget extraction</t>
+          <t>Prompt 4, strategy clean</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Two countries' budget figures come from a prompt version that has been superseded</t>
+          <t>Budget programme names come back out of stage 4 as plan strategies, then match 'their' programme perfectly</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Prompt 5 gained rules 3a and 4a on 2026-08-12 after Thailand's FY2024 was found to be missing programmes 2.14 and 2.15, whose table rows wrap and whose amounts are printed in the narrative. Only Thailand was re-run. Nothing in the pipeline compared an output's date with its prompt's, so the gap was invisible.</t>
+          <t>run_stage4 injects the budget programme list into Prompt 4 as the target granularity, which is right: it is how a strategy lands on a fundable unit. But nothing forbids the model from ANSWERING with a bucket name when it has no plan material to consolidate. Brunei's NDP text is a speech, stage 3 recovers little, and four strategies came back that are budget lines wearing a strategy's clothes.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Re-run stage 5 for Brazil (2021, 2024) and Brunei (2021, 2022, 2025, 2026), then run_pipeline for both. Detector D12 already reports the condition; promote it to a gate once both are current.</t>
+          <t>Two lines in Prompt 4: a strategy must consolidate at least one intervention from the row-level table, and the budget programme list is a target to map ONTO, never a source to draw names from. Check A18 already fails any strategyclean row with no component intervention, so the rule is enforced rather than hoped for. A18 is advisory today; promote it to a gate once Brunei is re-run.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>02_Automation/run_llm_pipeline.py --stages 5 --force, then 01_Pipeline/scripts/run_pipeline.py</t>
+          <t>01_Pipeline/prompts/4_strategy_clean.txt, 01_Pipeline/scripts/audit_checks.py (A18, already added)</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Six budget documents through stage 5. Brunei's four are speeches and will still extract poorly until F3 lands, so Brazil's two are the ones that will actually change figures.</t>
+          <t>Re-run stage 4 for Brunei. Thailand and Brazil already pass A18, so they need no re-run for this.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Brunei's two unreconciled strategy-years stay unexplained, and Brazil's coverage may be understated by whatever the old prompt skipped.</t>
+          <t>Brunei's page shows budget lines as plan strategies with confident rationales, and its 97.4% of budget mapped is partly the budget matching itself.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -747,14 +747,14 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W3, W6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>F8</t>
+          <t>F7</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -769,32 +769,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>A multi-year project table extracts nothing, because which column is this year's budget is never stated</t>
+          <t>Two countries' budget figures come from a prompt version that has been superseded</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Prompt 5 assumes a budget table has one amount column and a strategy total to reconcile against. Kiribati's development budget has six year columns and no ministry totals; Thailand's FY2023 book has three. Where the assumption holds the prompt works; where it does not the model correctly declines to guess and the country produces nothing for the price of a full extraction.</t>
+          <t>Prompt 5 gained rules 3a and 4a on 2026-08-12 after Thailand's FY2024 was found to be missing programmes 2.14 and 2.15, whose table rows wrap and whose amounts are printed in the narrative. Only Thailand was re-run. Nothing in the pipeline compared an output's date with its prompt's, so the gap was invisible.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Add an optional amount_column to the per-year budget config, passed into Prompt 5 as the column to read ('2025 Budget'), and have the prompt state that where several year columns exist it must use the named one and emit nothing rather than guess. Where no column is named and several exist, stop before spending: document_shape.py already reports the count. The reconciliation rule needs the same treatment, since a table with no printed strategy total cannot reconcile and should say so rather than fail.</t>
+          <t>Re-run stage 5 for Brazil (2021, 2024) and Brunei (2021, 2022, 2025, 2026), then run_pipeline for both. Detector D12 already reports the condition; promote it to a gate once both are current.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>01_Pipeline/prompts/5_budget_extraction.txt, 02_Automation/inputs/&lt;slug&gt;.json (amount_column), 02_Automation/stages.py (pass it through), 01_Pipeline/scripts/document_shape.py (already reports year columns)</t>
+          <t>02_Automation/run_llm_pipeline.py --stages 5 --force, then 01_Pipeline/scripts/run_pipeline.py</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>One prompt change plus a re-run of stage 5 for Kiribati, four documents, about $2.</t>
+          <t>Six budget documents through stage 5. Brunei's four are speeches and will still extract poorly until F3 lands, so Brazil's two are the ones that will actually change figures.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Kiribati cannot be run at all, and any country whose budget is published as a multi-year table has the same wall. On the evidence of these ten, that is a common publishing format rather than an oddity.</t>
+          <t>Brunei's two unreconciled strategy-years stay unexplained, and Brazil's coverage may be understated by whatever the old prompt skipped.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>F9</t>
+          <t>F8</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -821,37 +821,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>orchestration</t>
+          <t>Prompt 5, budget extraction</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Countries are committed to a full run before anyone knows whether their budget document can be extracted at all</t>
+          <t>A multi-year project table extracts nothing, because which column is this year's budget is never stated</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>The only gate before spending was a text heuristic, and it was wrong three times in a row: Malaysia read as prose because its programme codes are six digits, Kiribati read as a usable table when its rows are catering and cleaning, Bhutan read as a usable table when its rows are corporate accounts. Each fix made the heuristic smarter without making it right, because the question is what the PROMPT will find and only the prompt can answer that.</t>
+          <t>Prompt 5 assumes a budget table has one amount column and a strategy total to reconcile against. Kiribati's development budget has six year columns and no ministry totals; Thailand's FY2023 book has three. Where the assumption holds the prompt works; where it does not the model correctly declines to guess and the country produces nothing for the price of a full extraction.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Make stage5_probe.py a required step: one budget document, 4 to 10 calls, programme rows counted per page. Wire it into the orchestrator so a country with no probe result, or a failing one, does not start. Then route by document class, since the probe also tells you WHICH class: estimates table to Prompt 5, narrative to 5b (F3), multi-year project table to 5c or a named amount column (F8), fiscal report to nothing until the right document is sourced.</t>
+          <t>Add an optional amount_column to the per-year budget config, passed into Prompt 5 as the column to read ('2025 Budget'), and have the prompt state that where several year columns exist it must use the named one and emit nothing rather than guess. Where no column is named and several exist, stop before spending: document_shape.py already reports the count. The reconciliation rule needs the same treatment, since a table with no printed strategy total cannot reconcile and should say so rather than fail.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>02_Automation/stage5_probe.py (written), 02_Automation/run_llm_pipeline.py (gate on it), 02_Automation/inputs/&lt;slug&gt;.json (documents.style)</t>
+          <t>01_Pipeline/prompts/5_budget_extraction.txt, 02_Automation/inputs/&lt;slug&gt;.json (amount_column), 02_Automation/stages.py (pass it through), 01_Pipeline/scripts/document_shape.py (already reports year columns)</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>None to build; it saves $8 to $48 every time a country would have failed.</t>
+          <t>One prompt change plus a re-run of stage 5 for Kiribati, four documents, about $2.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Kiribati cost $6.21 and Bhutan $2.00 to learn what $0.60 of probing would have said first.</t>
+          <t>Kiribati cannot be run at all, and any country whose budget is published as a multi-year table has the same wall. On the evidence of these ten, that is a common publishing format rather than an oddity.</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -861,54 +861,54 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>W8, W9</t>
+          <t>W8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>F9</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Prompt 5, budget extraction</t>
+          <t>orchestration</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Brunei yields one usable budget year out of four documents, and budget line names leak into the strategy inventory</t>
+          <t>Countries are committed to a full run before anyone knows whether their budget document can be extracted at all</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Brunei's budget is a speech, not a table. Prompt 5 is written for a tabulated budget: it looks for programme rows with codes and amounts, finds few, and the gap is then filled from the budget side of the mapping, which puts budget line names into the strategy column.</t>
+          <t>The only gate before spending was a text heuristic, and it was wrong three times in a row: Malaysia read as prose because its programme codes are six digits, Kiribati read as a usable table when its rows are catering and cleaning, Bhutan read as a usable table when its rows are corporate accounts. Each fix made the heuristic smarter without making it right, because the question is what the PROMPT will find and only the prompt can answer that.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>A second budget-extraction prompt for narrative budgets, selected per country by a documents.style flag in the country config. It reads prose ('The amount of X million will be allocated to Y'), emits the same schema, and marks each row with the sentence it came from so source fidelity can still check it. China's budget has the same shape, so the prompt is needed twice over.</t>
+          <t>Make stage5_probe.py a required step: one budget document, 4 to 10 calls, programme rows counted per page. Wire it into the orchestrator so a country with no probe result, or a failing one, does not start. Then route by document class, since the probe also tells you WHICH class: estimates table to Prompt 5, narrative to 5b (F3), multi-year project table to 5c or a named amount column (F8), fiscal report to nothing until the right document is sourced.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>01_Pipeline/prompts/5b_budget_transcript.txt (new), 02_Automation/stages.py (stage 5 selects the prompt), 01_Pipeline/countries/*.json (documents.style)</t>
+          <t>02_Automation/stage5_probe.py (written), 02_Automation/run_llm_pipeline.py (gate on it), 02_Automation/inputs/&lt;slug&gt;.json (documents.style)</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>One new prompt plus a re-run of stage 5 for Brunei's four documents.</t>
+          <t>None to build; it saves $8 to $48 every time a country would have failed.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Brunei stays a one-year country and its 97.4% coverage figure keeps resting on a single speech.</t>
+          <t>Kiribati cost $6.21 and Bhutan $2.00 to learn what $0.60 of probing would have said first.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -918,54 +918,54 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>W3, W4</t>
+          <t>W8, W9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>F4</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Prompt 3, intervention extraction</t>
+          <t>Prompt 5, budget extraction</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11.5% of intervention_evidence quotations are paraphrases rather than the plan's own words</t>
+          <t>Brunei yields one usable budget year out of four documents, and budget line names leak into the strategy inventory</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Prompt 3 asks for evidence and does not say that the evidence must be a substring of the source. The model summarises where the sentence is long.</t>
+          <t>Brunei's budget is a speech, not a table. Prompt 5 is written for a tabulated budget: it looks for programme rows with codes and amounts, finds few, and the gap is then filled from the budget side of the mapping, which puts budget line names into the strategy column.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>State that intervention_evidence must be copied character for character, and that a quotation that cannot be copied verbatim should be shortened rather than reworded. validate_evidence_quotes already measures this, so the fix is verifiable the moment it runs.</t>
+          <t>A second budget-extraction prompt for narrative budgets, selected per country by a documents.style flag in the country config. It reads prose ('The amount of X million will be allocated to Y'), emits the same schema, and marks each row with the sentence it came from so source fidelity can still check it. China's budget has the same shape, so the prompt is needed twice over.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>01_Pipeline/prompts/3_strategy_extraction.txt</t>
+          <t>01_Pipeline/prompts/5b_budget_transcript.txt (new), 02_Automation/stages.py (stage 5 selects the prompt), 01_Pipeline/countries/*.json (documents.style)</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Re-run stage 3 per country.</t>
+          <t>One new prompt plus a re-run of stage 5 for Brunei's four documents.</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>A reviewer checking a quotation against the plan finds words that are not there and stops trusting the rest.</t>
+          <t>Brunei stays a one-year country and its 97.4% coverage figure keeps resting on a single speech.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -973,60 +973,117 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>W3, W4</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Prompt 3, intervention extraction</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11.5% of intervention_evidence quotations are paraphrases rather than the plan's own words</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Prompt 3 asks for evidence and does not say that the evidence must be a substring of the source. The model summarises where the sentence is long.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>State that intervention_evidence must be copied character for character, and that a quotation that cannot be copied verbatim should be shortened rather than reworded. validate_evidence_quotes already measures this, so the fix is verifiable the moment it runs.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>01_Pipeline/prompts/3_strategy_extraction.txt</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Re-run stage 3 per country.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>A reviewer checking a quotation against the plan finds words that are not there and stops trusting the rest.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>F5</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Supabase</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>maturity_summary has no view behind it, so the database cannot reproduce six of its eight metrics</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>0004_maturity_subtypes.sql was written and never applied: it needs either a service token or a paste into the SQL editor.</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Apply the migration, then confirm audit_checks A12 and build_dashboard_from_db --verify agree with the sheet.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>03_Ingest_and_Publishing/supabase/migrations/0004_maturity_subtypes.sql</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>None beyond applying it.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>The database round trip stays unfaithful for the maturity metrics.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>BLOCKED, needs a token or a paste</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1057,7 +1114,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-15 10:06 from 04_Docs_and_Planning/fixes.json</t>
+          <t>Generated 2026-08-15 10:22 from 04_Docs_and_Planning/fixes.json</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/FIXES.xlsx
+++ b/FIXES.xlsx
@@ -1114,7 +1114,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-15 10:22 from 04_Docs_and_Planning/fixes.json</t>
+          <t>Generated 2026-08-15 10:42 from 04_Docs_and_Planning/fixes.json</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/FIXES.xlsx
+++ b/FIXES.xlsx
@@ -1114,7 +1114,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-15 10:42 from 04_Docs_and_Planning/fixes.json</t>
+          <t>Generated 2026-08-15 15:17 from 04_Docs_and_Planning/fixes.json</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/FIXES.xlsx
+++ b/FIXES.xlsx
@@ -1114,7 +1114,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-15 15:17 from 04_Docs_and_Planning/fixes.json</t>
+          <t>Generated 2026-08-15 16:31 from 04_Docs_and_Planning/fixes.json</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/FIXES.xlsx
+++ b/FIXES.xlsx
@@ -1114,7 +1114,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-15 16:31 from 04_Docs_and_Planning/fixes.json</t>
+          <t>Generated 2026-08-15 21:30 from 04_Docs_and_Planning/fixes.json</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/FIXES.xlsx
+++ b/FIXES.xlsx
@@ -1114,7 +1114,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-15 21:30 from 04_Docs_and_Planning/fixes.json</t>
+          <t>Generated 2026-08-15 21:37 from 04_Docs_and_Planning/fixes.json</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/FIXES.xlsx
+++ b/FIXES.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED, needs a token or a paste</t>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
@@ -1114,7 +1114,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-15 21:37 from 04_Docs_and_Planning/fixes.json</t>
+          <t>Generated 2026-08-26 00:37 from 04_Docs_and_Planning/fixes.json</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/FIXES.xlsx
+++ b/FIXES.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fixes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="about" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'fixes'!$A$1:$K$11</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,34 +29,14 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="13"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00333333"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE5CD"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -70,19 +51,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -453,17 +425,17 @@
   <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="56" customWidth="1" min="5" max="5"/>
-    <col width="62" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="42" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
+    <col width="90" customWidth="1" min="5" max="5"/>
+    <col width="90" customWidth="1" min="6" max="6"/>
+    <col width="90" customWidth="1" min="7" max="7"/>
+    <col width="90" customWidth="1" min="8" max="8"/>
+    <col width="90" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -529,7 +501,7 @@
           <t>F1</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -574,56 +546,52 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>F10</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>combine_budget_years</t>
+          <t>Prompt 4, strategy clean</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>The programme code style is defaulted, and the wrong default silently unmaps a whole country</t>
+          <t>Standing functions are tagged as responses to risks they do not address, inflating every risk chart</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>normalize_program_code assumes hierarchical codes and prefixes a bare code with its strategy. Where codes are standalone the result matches nothing. It cost Brazil 524 edges, then Kenya 824 programme-years and Jamaica 254, each discovered separately after a full run.</t>
+          <t>Prompt 4 asks which of the eleven risks a strategy relates to and accepts topical adjacency. Nothing requires the plan to say the strategy responds to that risk, and nothing penalises tagging six risks at once.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Choose the style by measuring rather than defaulting: try both against the mapping's codes and take the one that resolves more, or refuse to build and say which style the codes look like. The evidence is already on disk at build time, so this needs no model call and no new input. Add a check that fails when more than a tenth of a country's matched codes are absent from its own budget layer.</t>
+          <t>Require, for each risk named, a verbatim quotation from that strategy's own text that states the connection, emitted in a risk_evidence field beside related_risks. Cap at three risks unless the plan explicitly names more. Say that a standing function of the state (defence, debt service, pensions, general administration) is not a risk response unless the plan frames it as one. Then a new check, A19, fails any related_risks entry with no quotation behind it, which makes the rule enforceable rather than hoped for.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>01_Pipeline/scripts/combine_budget_years.py (normalize_program_code), 01_Pipeline/scripts/audit_checks.py (new check)</t>
+          <t>01_Pipeline/prompts/4_strategy_clean.txt, 02_Automation/schemas.py (STAGE4_FIELDS), 01_Pipeline/scripts/audit_checks.py (A19), 01_Pipeline/scripts/build_final_panel.py (carry risk_evidence)</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>None. Deterministic, and it runs on data the pipeline already holds.</t>
+          <t>Re-run stage 4 for all three countries. Stage 4 is the judgement stage, so this is the expensive one; roughly the cost of a full re-run of consolidation per country.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Every new country is one silent default away from mapping nothing, and the symptom looks like a bad model rather than a bad join.</t>
+          <t>Every risk chart on every page overstates how much of the budget responds to each risk, and the error is invisible to every existing check.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -631,56 +599,52 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>W11</t>
-        </is>
-      </c>
+      <c r="K3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Prompt 4, strategy clean</t>
+          <t>Prompt 5, budget extraction</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Standing functions are tagged as responses to risks they do not address, inflating every risk chart</t>
+          <t>Brunei yields one usable budget year out of four documents, and budget line names leak into the strategy inventory</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Prompt 4 asks which of the eleven risks a strategy relates to and accepts topical adjacency. Nothing requires the plan to say the strategy responds to that risk, and nothing penalises tagging six risks at once.</t>
+          <t>Brunei's budget is a speech, not a table. Prompt 5 is written for a tabulated budget: it looks for programme rows with codes and amounts, finds few, and the gap is then filled from the budget side of the mapping, which puts budget line names into the strategy column.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Require, for each risk named, a verbatim quotation from that strategy's own text that states the connection, emitted in a risk_evidence field beside related_risks. Cap at three risks unless the plan explicitly names more. Say that a standing function of the state (defence, debt service, pensions, general administration) is not a risk response unless the plan frames it as one. Then a new check, A19, fails any related_risks entry with no quotation behind it, which makes the rule enforceable rather than hoped for.</t>
+          <t>A second budget-extraction prompt for narrative budgets, selected per country by a documents.style flag in the country config. It reads prose ('The amount of X million will be allocated to Y'), emits the same schema, and marks each row with the sentence it came from so source fidelity can still check it. China's budget has the same shape, so the prompt is needed twice over.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>01_Pipeline/prompts/4_strategy_clean.txt, 02_Automation/schemas.py (STAGE4_FIELDS), 01_Pipeline/scripts/audit_checks.py (A19), 01_Pipeline/scripts/build_final_panel.py (carry risk_evidence)</t>
+          <t>01_Pipeline/prompts/5b_budget_transcript.txt (new), 02_Automation/stages.py (stage 5 selects the prompt), 01_Pipeline/countries/*.json (documents.style)</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Re-run stage 4 for all three countries. Stage 4 is the judgement stage, so this is the expensive one; roughly the cost of a full re-run of consolidation per country.</t>
+          <t>One new prompt plus a re-run of stage 5 for Brunei's four documents.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Every risk chart on every page overstates how much of the budget responds to each risk, and the error is invisible to every existing check.</t>
+          <t>Brunei stays a one-year country and its 97.4% coverage figure keeps resting on a single speech.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -688,56 +652,52 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
+      <c r="K4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>F6</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Prompt 4, strategy clean</t>
+          <t>Prompt 3, intervention extraction</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Budget programme names come back out of stage 4 as plan strategies, then match 'their' programme perfectly</t>
+          <t>11.5% of intervention_evidence quotations are paraphrases rather than the plan's own words</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>run_stage4 injects the budget programme list into Prompt 4 as the target granularity, which is right: it is how a strategy lands on a fundable unit. But nothing forbids the model from ANSWERING with a bucket name when it has no plan material to consolidate. Brunei's NDP text is a speech, stage 3 recovers little, and four strategies came back that are budget lines wearing a strategy's clothes.</t>
+          <t>Prompt 3 asks for evidence and does not say that the evidence must be a substring of the source. The model summarises where the sentence is long.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Two lines in Prompt 4: a strategy must consolidate at least one intervention from the row-level table, and the budget programme list is a target to map ONTO, never a source to draw names from. Check A18 already fails any strategyclean row with no component intervention, so the rule is enforced rather than hoped for. A18 is advisory today; promote it to a gate once Brunei is re-run.</t>
+          <t>State that intervention_evidence must be copied character for character, and that a quotation that cannot be copied verbatim should be shortened rather than reworded. validate_evidence_quotes already measures this, so the fix is verifiable the moment it runs.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>01_Pipeline/prompts/4_strategy_clean.txt, 01_Pipeline/scripts/audit_checks.py (A18, already added)</t>
+          <t>01_Pipeline/prompts/3_strategy_extraction.txt</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Re-run stage 4 for Brunei. Thailand and Brazil already pass A18, so they need no re-run for this.</t>
+          <t>Re-run stage 3 per country.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Brunei's page shows budget lines as plan strategies with confident rationales, and its 97.4% of budget mapped is partly the budget matching itself.</t>
+          <t>A reviewer checking a quotation against the plan finds words that are not there and stops trusting the rest.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -745,113 +705,105 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>W3, W6</t>
-        </is>
-      </c>
+      <c r="K5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>F7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Prompt 5, budget extraction</t>
+          <t>Supabase</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Two countries' budget figures come from a prompt version that has been superseded</t>
+          <t>maturity_summary has no view behind it, so the database cannot reproduce six of its eight metrics</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Prompt 5 gained rules 3a and 4a on 2026-08-12 after Thailand's FY2024 was found to be missing programmes 2.14 and 2.15, whose table rows wrap and whose amounts are printed in the narrative. Only Thailand was re-run. Nothing in the pipeline compared an output's date with its prompt's, so the gap was invisible.</t>
+          <t>0004_maturity_subtypes.sql was written and never applied: it needs either a service token or a paste into the SQL editor.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Re-run stage 5 for Brazil (2021, 2024) and Brunei (2021, 2022, 2025, 2026), then run_pipeline for both. Detector D12 already reports the condition; promote it to a gate once both are current.</t>
+          <t>Apply the migration, then confirm audit_checks A12 and build_dashboard_from_db --verify agree with the sheet.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>02_Automation/run_llm_pipeline.py --stages 5 --force, then 01_Pipeline/scripts/run_pipeline.py</t>
+          <t>03_Ingest_and_Publishing/supabase/migrations/0004_maturity_subtypes.sql</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Six budget documents through stage 5. Brunei's four are speeches and will still extract poorly until F3 lands, so Brazil's two are the ones that will actually change figures.</t>
+          <t>None beyond applying it.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Brunei's two unreconciled strategy-years stay unexplained, and Brazil's coverage may be understated by whatever the old prompt skipped.</t>
+          <t>The database round trip stays unfaithful for the maturity metrics.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>F8</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+          <t>F6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Prompt 5, budget extraction</t>
+          <t>Prompt 4, strategy clean</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>A multi-year project table extracts nothing, because which column is this year's budget is never stated</t>
+          <t>Budget programme names come back out of stage 4 as plan strategies, then match 'their' programme perfectly</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Prompt 5 assumes a budget table has one amount column and a strategy total to reconcile against. Kiribati's development budget has six year columns and no ministry totals; Thailand's FY2023 book has three. Where the assumption holds the prompt works; where it does not the model correctly declines to guess and the country produces nothing for the price of a full extraction.</t>
+          <t>run_stage4 injects the budget programme list into Prompt 4 as the target granularity, which is right: it is how a strategy lands on a fundable unit. But nothing forbids the model from ANSWERING with a bucket name when it has no plan material to consolidate. Brunei's NDP text is a speech, stage 3 recovers little, and four strategies came back that are budget lines wearing a strategy's clothes.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Add an optional amount_column to the per-year budget config, passed into Prompt 5 as the column to read ('2025 Budget'), and have the prompt state that where several year columns exist it must use the named one and emit nothing rather than guess. Where no column is named and several exist, stop before spending: document_shape.py already reports the count. The reconciliation rule needs the same treatment, since a table with no printed strategy total cannot reconcile and should say so rather than fail.</t>
+          <t>Two lines in Prompt 4: a strategy must consolidate at least one intervention from the row-level table, and the budget programme list is a target to map ONTO, never a source to draw names from. Check A18 already fails any strategyclean row with no component intervention, so the rule is enforced rather than hoped for. A18 is advisory today; promote it to a gate once Brunei is re-run.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>01_Pipeline/prompts/5_budget_extraction.txt, 02_Automation/inputs/&lt;slug&gt;.json (amount_column), 02_Automation/stages.py (pass it through), 01_Pipeline/scripts/document_shape.py (already reports year columns)</t>
+          <t>01_Pipeline/prompts/4_strategy_clean.txt, 01_Pipeline/scripts/audit_checks.py (A18, already added)</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>One prompt change plus a re-run of stage 5 for Kiribati, four documents, about $2.</t>
+          <t>Re-run stage 4 for Brunei. Thailand and Brazil already pass A18, so they need no re-run for this.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Kiribati cannot be run at all, and any country whose budget is published as a multi-year table has the same wall. On the evidence of these ten, that is a common publishing format rather than an oddity.</t>
+          <t>Brunei's page shows budget lines as plan strategies with confident rationales, and its 97.4% of budget mapped is partly the budget matching itself.</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -859,56 +811,52 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
+      <c r="K7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>F9</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>orchestration</t>
+          <t>Prompt 5, budget extraction</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Countries are committed to a full run before anyone knows whether their budget document can be extracted at all</t>
+          <t>Two countries' budget figures come from a prompt version that has been superseded</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>The only gate before spending was a text heuristic, and it was wrong three times in a row: Malaysia read as prose because its programme codes are six digits, Kiribati read as a usable table when its rows are catering and cleaning, Bhutan read as a usable table when its rows are corporate accounts. Each fix made the heuristic smarter without making it right, because the question is what the PROMPT will find and only the prompt can answer that.</t>
+          <t>Prompt 5 gained rules 3a and 4a on 2026-08-12 after Thailand's FY2024 was found to be missing programmes 2.14 and 2.15, whose table rows wrap and whose amounts are printed in the narrative. Only Thailand was re-run. Nothing in the pipeline compared an output's date with its prompt's, so the gap was invisible.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Make stage5_probe.py a required step: one budget document, 4 to 10 calls, programme rows counted per page. Wire it into the orchestrator so a country with no probe result, or a failing one, does not start. Then route by document class, since the probe also tells you WHICH class: estimates table to Prompt 5, narrative to 5b (F3), multi-year project table to 5c or a named amount column (F8), fiscal report to nothing until the right document is sourced.</t>
+          <t>Re-run stage 5 for Brazil (2021, 2024) and Brunei (2021, 2022, 2025, 2026), then run_pipeline for both. Detector D12 already reports the condition; promote it to a gate once both are current.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>02_Automation/stage5_probe.py (written), 02_Automation/run_llm_pipeline.py (gate on it), 02_Automation/inputs/&lt;slug&gt;.json (documents.style)</t>
+          <t>02_Automation/run_llm_pipeline.py --stages 5 --force, then 01_Pipeline/scripts/run_pipeline.py</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>None to build; it saves $8 to $48 every time a country would have failed.</t>
+          <t>Six budget documents through stage 5. Brunei's four are speeches and will still extract poorly until F3 lands, so Brazil's two are the ones that will actually change figures.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Kiribati cost $6.21 and Bhutan $2.00 to learn what $0.60 of probing would have said first.</t>
+          <t>Brunei's two unreconciled strategy-years stay unexplained, and Brazil's coverage may be understated by whatever the old prompt skipped.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -916,21 +864,17 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>W8, W9</t>
-        </is>
-      </c>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>F8</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -940,32 +884,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Brunei yields one usable budget year out of four documents, and budget line names leak into the strategy inventory</t>
+          <t>A multi-year project table extracts nothing, because which column is this year's budget is never stated</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Brunei's budget is a speech, not a table. Prompt 5 is written for a tabulated budget: it looks for programme rows with codes and amounts, finds few, and the gap is then filled from the budget side of the mapping, which puts budget line names into the strategy column.</t>
+          <t>Prompt 5 assumes a budget table has one amount column and a strategy total to reconcile against. Kiribati's development budget has six year columns and no ministry totals; Thailand's FY2023 book has three. Where the assumption holds the prompt works; where it does not the model correctly declines to guess and the country produces nothing for the price of a full extraction.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>A second budget-extraction prompt for narrative budgets, selected per country by a documents.style flag in the country config. It reads prose ('The amount of X million will be allocated to Y'), emits the same schema, and marks each row with the sentence it came from so source fidelity can still check it. China's budget has the same shape, so the prompt is needed twice over.</t>
+          <t>Add an optional amount_column to the per-year budget config, passed into Prompt 5 as the column to read ('2025 Budget'), and have the prompt state that where several year columns exist it must use the named one and emit nothing rather than guess. Where no column is named and several exist, stop before spending: document_shape.py already reports the count. The reconciliation rule needs the same treatment, since a table with no printed strategy total cannot reconcile and should say so rather than fail.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>01_Pipeline/prompts/5b_budget_transcript.txt (new), 02_Automation/stages.py (stage 5 selects the prompt), 01_Pipeline/countries/*.json (documents.style)</t>
+          <t>01_Pipeline/prompts/5_budget_extraction.txt, 02_Automation/inputs/&lt;slug&gt;.json (amount_column), 02_Automation/stages.py (pass it through), 01_Pipeline/scripts/document_shape.py (already reports year columns)</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>One new prompt plus a re-run of stage 5 for Brunei's four documents.</t>
+          <t>One prompt change plus a re-run of stage 5 for Kiribati, four documents, about $2.</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Brunei stays a one-year country and its 97.4% coverage figure keeps resting on a single speech.</t>
+          <t>Kiribati cannot be run at all, and any country whose budget is published as a multi-year table has the same wall. On the evidence of these ten, that is a common publishing format rather than an oddity.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -973,56 +917,52 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>W3, W4</t>
-        </is>
-      </c>
+      <c r="K9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F9</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Prompt 3, intervention extraction</t>
+          <t>orchestration</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11.5% of intervention_evidence quotations are paraphrases rather than the plan's own words</t>
+          <t>Countries are committed to a full run before anyone knows whether their budget document can be extracted at all</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Prompt 3 asks for evidence and does not say that the evidence must be a substring of the source. The model summarises where the sentence is long.</t>
+          <t>The only gate before spending was a text heuristic, and it was wrong three times in a row: Malaysia read as prose because its programme codes are six digits, Kiribati read as a usable table when its rows are catering and cleaning, Bhutan read as a usable table when its rows are corporate accounts. Each fix made the heuristic smarter without making it right, because the question is what the PROMPT will find and only the prompt can answer that.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>State that intervention_evidence must be copied character for character, and that a quotation that cannot be copied verbatim should be shortened rather than reworded. validate_evidence_quotes already measures this, so the fix is verifiable the moment it runs.</t>
+          <t>Make stage5_probe.py a required step: one budget document, 4 to 10 calls, programme rows counted per page. Wire it into the orchestrator so a country with no probe result, or a failing one, does not start. Then route by document class, since the probe also tells you WHICH class: estimates table to Prompt 5, narrative to 5b (F3), multi-year project table to 5c or a named amount column (F8), fiscal report to nothing until the right document is sourced.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>01_Pipeline/prompts/3_strategy_extraction.txt</t>
+          <t>02_Automation/stage5_probe.py (written), 02_Automation/run_llm_pipeline.py (gate on it), 02_Automation/inputs/&lt;slug&gt;.json (documents.style)</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Re-run stage 3 per country.</t>
+          <t>None to build; it saves $8 to $48 every time a country would have failed.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>A reviewer checking a quotation against the plan finds words that are not there and stops trusting the rest.</t>
+          <t>Kiribati cost $6.21 and Bhutan $2.00 to learn what $0.60 of probing would have said first.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1035,163 +975,58 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>F10</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>combine_budget_years</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>maturity_summary has no view behind it, so the database cannot reproduce six of its eight metrics</t>
+          <t>The programme code style is defaulted, and the wrong default silently unmaps a whole country</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0004_maturity_subtypes.sql was written and never applied: it needs either a service token or a paste into the SQL editor.</t>
+          <t>normalize_program_code assumes hierarchical codes and prefixes a bare code with its strategy. Where codes are standalone the result matches nothing. It cost Brazil 524 edges, then Kenya 824 programme-years and Jamaica 254, each discovered separately after a full run.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Apply the migration, then confirm audit_checks A12 and build_dashboard_from_db --verify agree with the sheet.</t>
+          <t>Choose the style by measuring rather than defaulting: try both against the mapping's codes and take the one that resolves more, or refuse to build and say which style the codes look like. The evidence is already on disk at build time, so this needs no model call and no new input. Add a check that fails when more than a tenth of a country's matched codes are absent from its own budget layer.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>03_Ingest_and_Publishing/supabase/migrations/0004_maturity_subtypes.sql</t>
+          <t>01_Pipeline/scripts/combine_budget_years.py (normalize_program_code), 01_Pipeline/scripts/audit_checks.py (new check)</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>None beyond applying it.</t>
+          <t>None. Deterministic, and it runs on data the pipeline already holds.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>The database round trip stays unfaithful for the maturity metrics.</t>
+          <t>Every new country is one silent default away from mapping nothing, and the symptom looks like a bad model rather than a bad join.</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>FIXED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="104" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>AI Unveils Tomorrow - fix register</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Generated 2026-08-26 00:37 from 04_Docs_and_Planning/fixes.json</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Priority 1</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Changes a number people read. Do these before the next country.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Priority 2</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Changes what the pipeline can handle at all.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Priority 3</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Changes how much the output can be trusted, not what it says.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>DATA ISSUE</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>The entry in DATA_ISSUES.xlsx this fix closes. A fix with no data issue behind it is a fix nobody has evidence for.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="2" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Not in here</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Contract violations, which are in Prompt Output Issues.docx and are generated from the L2 reports rather than typed.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <autoFilter ref="A1:K11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>